--- a/inventories/baseline/lci-Salar-del-Hombre-Muerto-North.xlsx
+++ b/inventories/baseline/lci-Salar-del-Hombre-Muerto-North.xlsx
@@ -818,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="B27">
-        <v>-0.007317182565765824</v>
+        <v>-0.007317182565765822</v>
       </c>
       <c r="C27" t="s">
         <v>1</v>
@@ -869,7 +869,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.01198801479127035</v>
+        <v>0.01198801479127034</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
@@ -903,7 +903,7 @@
         <v>34</v>
       </c>
       <c r="B32">
-        <v>0.003322457008335009</v>
+        <v>0.003322457008335008</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -920,7 +920,7 @@
         <v>35</v>
       </c>
       <c r="B33">
-        <v>0.0004456977284032338</v>
+        <v>0.0004456977284032337</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -937,7 +937,7 @@
         <v>36</v>
       </c>
       <c r="B34">
-        <v>-0.00835714606118099</v>
+        <v>-0.008357146061180988</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
@@ -1201,7 +1201,7 @@
         <v>3</v>
       </c>
       <c r="B60">
-        <v>0.05496766668214976</v>
+        <v>0.05274572414992727</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1218,7 +1218,7 @@
         <v>41</v>
       </c>
       <c r="B61">
-        <v>0.9312904166473127</v>
+        <v>0.934067844812591</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         <v>28</v>
       </c>
       <c r="B62">
-        <v>0.2554244993910952</v>
+        <v>0.2561862630536752</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
@@ -1252,7 +1252,7 @@
         <v>42</v>
       </c>
       <c r="B63">
-        <v>0.01374191667053744</v>
+        <v>0.01318643103748182</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="B75">
-        <v>0.0005860508005212913</v>
+        <v>0.0005860508005212914</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -1384,7 +1384,7 @@
         <v>44</v>
       </c>
       <c r="B76">
-        <v>0.9975896281979559</v>
+        <v>0.9975896281979558</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -1831,7 +1831,7 @@
         <v>40</v>
       </c>
       <c r="B118">
-        <v>90.466454147623</v>
+        <v>94.27740310034936</v>
       </c>
       <c r="C118" t="s">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>0.09751773664337471</v>
+        <v>0.1016257247350366</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -1865,7 +1865,7 @@
         <v>49</v>
       </c>
       <c r="B120">
-        <v>-0.01921246266550721</v>
+        <v>-0.01984557596732152</v>
       </c>
       <c r="C120" t="s">
         <v>1</v>
@@ -1980,7 +1980,7 @@
         <v>26</v>
       </c>
       <c r="B132">
-        <v>1.052631578947368</v>
+        <v>1.052631578947369</v>
       </c>
       <c r="C132" t="s">
         <v>1</v>
@@ -1997,7 +1997,7 @@
         <v>22</v>
       </c>
       <c r="B133">
-        <v>0.0005263157894736842</v>
+        <v>0.0005263157894736843</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -2014,7 +2014,7 @@
         <v>36</v>
       </c>
       <c r="B134">
-        <v>-0.05263157894736842</v>
+        <v>-0.05263157894736843</v>
       </c>
       <c r="C134" t="s">
         <v>31</v>
@@ -2708,7 +2708,7 @@
         <v>54</v>
       </c>
       <c r="B201">
-        <v>0.02233578483480478</v>
+        <v>0.02136918144074027</v>
       </c>
       <c r="D201" t="s">
         <v>11</v>
@@ -2725,7 +2725,7 @@
         <v>55</v>
       </c>
       <c r="B202">
-        <v>2.665092645174623E-10</v>
+        <v>2.549758099494904E-10</v>
       </c>
       <c r="D202" t="s">
         <v>56</v>
@@ -2742,7 +2742,7 @@
         <v>58</v>
       </c>
       <c r="B203">
-        <v>8.883642150582077E-12</v>
+        <v>8.499193664983014E-12</v>
       </c>
       <c r="D203" t="s">
         <v>59</v>
@@ -2759,7 +2759,7 @@
         <v>60</v>
       </c>
       <c r="B204">
-        <v>8.883642150582077E-12</v>
+        <v>8.499193664983014E-12</v>
       </c>
       <c r="D204" t="s">
         <v>59</v>
@@ -2810,7 +2810,7 @@
         <v>3</v>
       </c>
       <c r="B207">
-        <v>1.314676458666168</v>
+        <v>1.301058520669875</v>
       </c>
       <c r="C207" t="s">
         <v>1</v>
@@ -2827,7 +2827,7 @@
         <v>61</v>
       </c>
       <c r="B208">
-        <v>7.583144132845589E-05</v>
+        <v>7.254975997689348E-05</v>
       </c>
       <c r="C208" t="s">
         <v>1</v>
@@ -2844,7 +2844,7 @@
         <v>22</v>
       </c>
       <c r="B209">
-        <v>0.005532795132802963</v>
+        <v>0.005300185256383684</v>
       </c>
       <c r="C209" t="s">
         <v>23</v>
@@ -2861,7 +2861,7 @@
         <v>45</v>
       </c>
       <c r="B210">
-        <v>1.267093054093207E-09</v>
+        <v>0.1347141132054436</v>
       </c>
       <c r="C210" t="s">
         <v>31</v>
@@ -2878,7 +2878,7 @@
         <v>63</v>
       </c>
       <c r="B211">
-        <v>0.002366417624866422</v>
+        <v>0.002264008538958429</v>
       </c>
       <c r="C211" t="s">
         <v>31</v>
@@ -2895,7 +2895,7 @@
         <v>64</v>
       </c>
       <c r="B212">
-        <v>-8.444802077834694</v>
+        <v>-8.079344834625653</v>
       </c>
       <c r="C212" t="s">
         <v>31</v>
@@ -2912,7 +2912,7 @@
         <v>49</v>
       </c>
       <c r="B213">
-        <v>-0.001314676458259123</v>
+        <v>-0.001257782521643572</v>
       </c>
       <c r="C213" t="s">
         <v>1</v>
